--- a/AAII_Financials/Quarterly/FIP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FIP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="92">
   <si>
     <t>FIP</t>
   </si>
@@ -656,236 +656,243 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>186800</v>
+      </c>
+      <c r="E8" s="3">
         <v>188400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>143500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>140600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>122300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>96200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>80800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>83300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>84900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>82500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>81400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>80700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>81800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>76500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>71400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>78600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>65900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>46100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>47500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>72700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>15300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>20500</v>
       </c>
-      <c r="Y8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>117300</v>
+      </c>
+      <c r="E9" s="3">
         <v>120400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>83100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>75000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>74400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>67000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>59100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>62800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>61200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>64600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>57300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>68400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>62800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>65200</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R9" s="3" t="s">
         <v>3</v>
       </c>
@@ -913,53 +920,56 @@
       <c r="Z9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>69400</v>
+      </c>
+      <c r="E10" s="3">
         <v>68000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>60400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>65600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>47900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>29100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>21700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>20500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>23700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>18000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>24100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>12300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>19100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>11300</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>3</v>
       </c>
@@ -987,8 +997,11 @@
       <c r="Z10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1015,8 +1028,9 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1089,8 +1103,11 @@
       <c r="Z12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1163,156 +1180,165 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>104700</v>
+      </c>
+      <c r="E14" s="3">
         <v>90500</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>34900</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>83700</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>38100</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-94500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>93400</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>16000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>27900</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>17900</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>12600</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>18900</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>15800</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>15100</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>1000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>2800</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>8900</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>4200</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>6000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>8900</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>2600</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>1000</v>
       </c>
-      <c r="Y14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>39500</v>
+      </c>
+      <c r="E15" s="3">
         <v>50700</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>38700</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>34800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>34000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>25000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>19200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>19500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>20200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>20500</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>20400</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>20200</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>20300</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>20100</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>18300</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>18100</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>17300</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>17000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>15100</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>38900</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>11700</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>10100</v>
       </c>
-      <c r="Y15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1336,156 +1362,163 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>164200</v>
+      </c>
+      <c r="E17" s="3">
         <v>178700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>137500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>116400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>116000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>99700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>61100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>87800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>87000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>93000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>88600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>94800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>89900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>91500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>85000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>87700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>81000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>65900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>60400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>131400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>37000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>33500</v>
       </c>
-      <c r="Y17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>22600</v>
+      </c>
+      <c r="E18" s="3">
         <v>9600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>6000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>24100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>6300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-3600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>19700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-4400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-2100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-10400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-7200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-14100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-8000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-15000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-13600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-9100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-15100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-19800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-12900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-58700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-21700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-13000</v>
       </c>
-      <c r="Y18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1512,378 +1545,394 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E20" s="3">
         <v>-2500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-21500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-8100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-1100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-9000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>35600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>8100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>5800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>9500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>10600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>7000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-4600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-21900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-13400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-14400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-22500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-6700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-15700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-7500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-200</v>
       </c>
-      <c r="Y20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>64800</v>
+      </c>
+      <c r="E21" s="3">
         <v>62800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>66100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>67100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>41400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>30500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>3400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>7000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>12200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-1000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>12000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>9700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-17300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-4300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-12200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-25200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-4500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-35500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-17600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-3100</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>105500</v>
+      </c>
+      <c r="E22" s="3">
         <v>82500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>90300</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>73300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>59200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>43100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>33300</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>31500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>29700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>27600</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>26200</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>26000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>24200</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>23300</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>21100</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>19200</v>
-      </c>
-      <c r="S22" s="3">
-        <v>6500</v>
       </c>
       <c r="T22" s="3">
         <v>6500</v>
       </c>
       <c r="U22" s="3">
+        <v>6500</v>
+      </c>
+      <c r="V22" s="3">
         <v>6600</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>9400</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>3500</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>1500</v>
       </c>
-      <c r="Y22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-184900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-160900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-97700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-124800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-90000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>56800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-142600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-60000</v>
-      </c>
-      <c r="K23" s="3">
-        <v>-65500</v>
       </c>
       <c r="L23" s="3">
         <v>-65500</v>
       </c>
       <c r="M23" s="3">
+        <v>-65500</v>
+      </c>
+      <c r="N23" s="3">
         <v>-56600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-66000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-48300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-48800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-56700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-41600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-36000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-48700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-26200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-83800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-32800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-14700</v>
       </c>
-      <c r="Y23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-11600</v>
+      </c>
+      <c r="E24" s="3">
         <v>3500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>32200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>5100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-41500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-100</v>
       </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
       <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3">
         <v>800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-2800</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-400</v>
       </c>
-      <c r="Y24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1956,156 +2005,165 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-173300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-164400</v>
-      </c>
-      <c r="E26" s="3">
-        <v>-129800</v>
       </c>
       <c r="F26" s="3">
         <v>-129800</v>
       </c>
       <c r="G26" s="3">
+        <v>-129800</v>
+      </c>
+      <c r="H26" s="3">
         <v>-90900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>98300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-143900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-59900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-65800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-67300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-56500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-66000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-49100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-50500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-56100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-43200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-38000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-50300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-25300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-81000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-32100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-14300</v>
       </c>
-      <c r="Y26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-166500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-154500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-123300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-159200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-83900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>108300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-133600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-50000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-54400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-56600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-48200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-56100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-38900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-40600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-60900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-44100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-29500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-42800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-17800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-62100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-25400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-9300</v>
       </c>
-      <c r="Y27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2178,8 +2236,11 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2252,8 +2313,11 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2326,8 +2390,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2400,156 +2467,165 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E32" s="3">
         <v>2500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>21500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>8100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>1100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>9000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-35600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-8100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-5800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-9500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-10600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-7000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>4600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>21900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>13400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>14400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>22500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>6700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>15700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>7500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>200</v>
       </c>
-      <c r="Y32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-162000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-150200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-119000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-118400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-79800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>109700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-133600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-50000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-54400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-56600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-48200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-56100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-38900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-40600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-60900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-44100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-29500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-42800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-17800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-62100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-25400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-9300</v>
       </c>
-      <c r="Y33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2622,161 +2698,170 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-162000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-150200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-119000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-118400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-79800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>109700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-133600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-50000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-54400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-56600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-48200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-56100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-38900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-40600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-60900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-44100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-29500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-42800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-17800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-62100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-25400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-9300</v>
       </c>
-      <c r="Y35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2803,8 +2888,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2831,71 +2917,72 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>32600</v>
+      </c>
+      <c r="E41" s="3">
         <v>37900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>57400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>34700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>33600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>26300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>27800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>20300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>33100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>23000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>29400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>24400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>42500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>40000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>36500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>69500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>68500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>65500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>49900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>55200</v>
       </c>
-      <c r="W41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2905,8 +2992,11 @@
       <c r="Z41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2941,17 +3031,17 @@
         <v>0</v>
       </c>
       <c r="N42" s="3">
+        <v>0</v>
+      </c>
+      <c r="O42" s="3">
         <v>1900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>19700</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>21600</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
-      </c>
       <c r="R42" s="3">
         <v>0</v>
       </c>
@@ -2979,71 +3069,74 @@
       <c r="Z42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>106300</v>
+      </c>
+      <c r="E43" s="3">
         <v>133500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>119600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>65600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>70900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>66600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>53400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>84100</v>
-      </c>
-      <c r="K43" s="3">
-        <v>83800</v>
       </c>
       <c r="L43" s="3">
         <v>83800</v>
       </c>
       <c r="M43" s="3">
+        <v>83800</v>
+      </c>
+      <c r="N43" s="3">
         <v>83100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>86100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>77800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>91800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>80800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>98100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>93600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>36500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>50300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>85800</v>
       </c>
-      <c r="W43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3053,40 +3146,43 @@
       <c r="Z43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>900</v>
+      </c>
+      <c r="E44" s="3">
         <v>1000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1300</v>
       </c>
-      <c r="F44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H44" s="3">
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3">
         <v>400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>300</v>
       </c>
-      <c r="J44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M44" s="3">
-        <v>300</v>
+      <c r="M44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N44" s="3">
         <v>300</v>
@@ -3095,20 +3191,20 @@
         <v>300</v>
       </c>
       <c r="P44" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q44" s="3">
         <v>900</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>3600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>4600</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>5900</v>
       </c>
-      <c r="T44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3121,77 +3217,80 @@
       <c r="X44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y44" s="3">
-        <v>0</v>
+      <c r="Y44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>71900</v>
+      </c>
+      <c r="E45" s="3">
         <v>16900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>16800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>13800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>7900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>11900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>9100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>10700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>8200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>7100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>5700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>5500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>5400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>156900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>180300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>259600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>276000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>312800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>346600</v>
       </c>
-      <c r="W45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3201,71 +3300,74 @@
       <c r="Z45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>367800</v>
+      </c>
+      <c r="E46" s="3">
         <v>397600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>484000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>442800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>539000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>318700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>219900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>247100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>289200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>164500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>185500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>180000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>214400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>239100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>277800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>352500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>427600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>378000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>413000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>487700</v>
       </c>
-      <c r="W46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3275,71 +3377,74 @@
       <c r="Z46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>21200</v>
+      </c>
+      <c r="E47" s="3">
         <v>21700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>27200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1137400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>22700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>19100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>12500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>59100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>68500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>68100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>72700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>70100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>70200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>72300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>84400</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>84500</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>86900</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>55400</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>54400</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>89300</v>
       </c>
-      <c r="W47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3349,71 +3454,74 @@
       <c r="Z47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3325800</v>
+      </c>
+      <c r="E48" s="3">
         <v>4761900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>4751800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3360500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3336700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3291900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1758900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1729900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1710200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1715300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1736200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1766800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1791700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1790000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1779700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1747100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1704600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1654000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1625200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1599000</v>
       </c>
-      <c r="W48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3423,71 +3531,74 @@
       <c r="Z48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>331300</v>
+      </c>
+      <c r="E49" s="3">
         <v>407900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>408900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>445400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>446500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>449700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>321600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>322600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>324200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>326100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>328000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>329900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>316700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>318600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>320400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>325200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>326800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>323800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>324900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>312000</v>
       </c>
-      <c r="W49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3497,8 +3608,11 @@
       <c r="Z49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3571,8 +3685,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3645,71 +3762,74 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1675000</v>
+      </c>
+      <c r="E52" s="3">
         <v>73200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>29700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>37800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>33300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>33200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>22200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>26300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>28000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>34100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>19500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>27600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>33700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>16300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>16000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>16100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>14300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>26500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>24900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>20300</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3719,8 +3839,11 @@
       <c r="Z52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3793,71 +3916,74 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5746700</v>
+      </c>
+      <c r="E54" s="3">
         <v>5688500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>5748700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>5451700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4407000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>4141900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2374400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2437500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2452400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2344700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2379600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2385100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2437600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2447100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2478400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2525500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2560200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>2437700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>2442300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>2508300</v>
       </c>
-      <c r="W54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3867,8 +3993,11 @@
       <c r="Z54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3895,8 +4024,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3923,71 +4053,72 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>222200</v>
+      </c>
+      <c r="E57" s="3">
         <v>243700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>259400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>186200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>212400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>204900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>166800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>144600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>107500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>135000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>118800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>124900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>122500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>132700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>136000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>150900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>162100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>92000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>115600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>128200</v>
       </c>
-      <c r="W57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3997,71 +4128,74 @@
       <c r="Z57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>487800</v>
+      </c>
+      <c r="E58" s="3">
         <v>36500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>74500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1522200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>90000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>98500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>55800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>7300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>7200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>84900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>7200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>6900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>31100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>7100</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R58" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T58" s="3">
-        <v>0</v>
+      <c r="T58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U58" s="3">
         <v>0</v>
       </c>
       <c r="V58" s="3">
+        <v>0</v>
+      </c>
+      <c r="W58" s="3">
         <v>25000</v>
       </c>
-      <c r="W58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4071,71 +4205,74 @@
       <c r="Z58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>610500</v>
+      </c>
+      <c r="E59" s="3">
         <v>73800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>61200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>51300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>49500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>58100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>17700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>16300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>20200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>16800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>14500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>19300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>15400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>6700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>23500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>20900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>12800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>11300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>13800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>15800</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4145,71 +4282,74 @@
       <c r="Z59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1334000</v>
+      </c>
+      <c r="E60" s="3">
         <v>361700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>410000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1770700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>362800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>371100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>250800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>173700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>137600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>239800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>150600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>162400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>182100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>154700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>159600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>171800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>174900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>103200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>129500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>169000</v>
       </c>
-      <c r="W60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4219,71 +4359,74 @@
       <c r="Z60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2404900</v>
+      </c>
+      <c r="E61" s="3">
         <v>3923200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>3779700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2275000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>3061200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2723800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1612100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1597300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1615200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1328100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1403400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1379800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1338800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1336800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1230200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1191900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>729400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>728600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>718600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>693000</v>
       </c>
-      <c r="W61" s="3">
-        <v>0</v>
-      </c>
       <c r="X61" s="3">
         <v>0</v>
       </c>
@@ -4293,71 +4436,74 @@
       <c r="Z61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1080200</v>
+      </c>
+      <c r="E62" s="3">
         <v>281700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>314700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>327300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>207000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>180500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>45500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>46400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>53100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>114100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>81700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>62100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>90900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>156000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>299300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>354000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>310100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>256100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>132200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>113200</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4367,8 +4513,11 @@
       <c r="Z62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4441,8 +4590,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4515,8 +4667,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4589,71 +4744,74 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5108400</v>
+      </c>
+      <c r="E66" s="3">
         <v>4868500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4804700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4372900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3631000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3275400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1918000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1817400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1805900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1681900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1641500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1604300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1611800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1647500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1662200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1699900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1203700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1081100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>980200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>981900</v>
       </c>
-      <c r="W66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4663,8 +4821,11 @@
       <c r="Z66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4691,8 +4852,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4765,8 +4927,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4839,13 +5004,16 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
-        <v>152600</v>
+        <v>153300</v>
       </c>
       <c r="E70" s="3">
         <v>152600</v>
@@ -4854,44 +5022,44 @@
         <v>152600</v>
       </c>
       <c r="G70" s="3">
+        <v>152600</v>
+      </c>
+      <c r="H70" s="3">
         <v>550300</v>
       </c>
-      <c r="H70" s="3">
+      <c r="I70" s="3">
         <v>529300</v>
       </c>
-      <c r="I70" s="3">
+      <c r="J70" s="3">
         <v>381200</v>
       </c>
-      <c r="J70" s="3">
+      <c r="K70" s="3">
         <v>366900</v>
       </c>
-      <c r="K70" s="3">
+      <c r="L70" s="3">
         <v>359800</v>
       </c>
-      <c r="L70" s="3">
+      <c r="M70" s="3">
         <v>342200</v>
       </c>
-      <c r="M70" s="3">
+      <c r="N70" s="3">
         <v>325200</v>
       </c>
-      <c r="N70" s="3">
+      <c r="O70" s="3">
         <v>310400</v>
       </c>
-      <c r="O70" s="3">
+      <c r="P70" s="3">
         <v>294400</v>
       </c>
-      <c r="P70" s="3">
+      <c r="Q70" s="3">
         <v>279200</v>
       </c>
-      <c r="Q70" s="3">
+      <c r="R70" s="3">
         <v>264600</v>
       </c>
-      <c r="R70" s="3">
+      <c r="S70" s="3">
         <v>252000</v>
       </c>
-      <c r="S70" s="3">
-        <v>0</v>
-      </c>
       <c r="T70" s="3">
         <v>0</v>
       </c>
@@ -4913,8 +5081,11 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4987,71 +5158,74 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-754000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-625900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-513000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-438600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-333100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-274300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-405800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-291500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-258500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-221800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-182200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-150600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-110500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-86900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-60800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-14400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>1656700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>1609000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>1617600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>1631600</v>
       </c>
-      <c r="W72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5061,8 +5235,11 @@
       <c r="Z72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5135,8 +5312,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5209,8 +5389,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5283,71 +5466,74 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-329800</v>
+      </c>
+      <c r="E76" s="3">
         <v>-122500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>21300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>181100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>375500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>476200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>202700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>370800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>394800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>402500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>484300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>533900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>580500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>559800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>551600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>573600</v>
-      </c>
-      <c r="S76" s="3">
-        <v>1356600</v>
       </c>
       <c r="T76" s="3">
         <v>1356600</v>
       </c>
       <c r="U76" s="3">
+        <v>1356600</v>
+      </c>
+      <c r="V76" s="3">
         <v>1462100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1526400</v>
       </c>
-      <c r="W76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5357,8 +5543,11 @@
       <c r="Z76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5431,161 +5620,170 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-162000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-150200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-119000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-118400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-79800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>109700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-133600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-50000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-54400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-56600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-48200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-56100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-38900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-40600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-60900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-44100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-29500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-42800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-17800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-62100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-25400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-9300</v>
       </c>
-      <c r="Y81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5612,82 +5810,86 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>33000</v>
+      </c>
+      <c r="E83" s="3">
         <v>24000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>18200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>17900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>18300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>18600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>18500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>18300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>18400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>18200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>16400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>16200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>15400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>15100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>18300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>18100</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>17300</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>17000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>15100</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>38900</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>11700</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>10100</v>
       </c>
-      <c r="Y83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5760,8 +5962,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5834,8 +6039,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5908,8 +6116,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5982,8 +6193,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6056,82 +6270,88 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>39000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-69400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-2800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-24400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-5200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-85700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-8100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>14200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-17600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-3900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>7700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>14700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-4800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-12100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-5000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>17700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-41200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-14100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>8100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-69800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-24200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-33600</v>
       </c>
-      <c r="Y89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6158,82 +6378,86 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-82600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-46500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-66000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-66400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-82400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-66500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-27900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-26300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-15400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-13300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-22000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-13000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-25800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-39900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-44900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-58300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-62200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-51700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-43400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-23500</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-42200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-31800</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6306,8 +6530,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6380,82 +6607,88 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-133400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-44800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-45800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1175200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-85900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>164300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-28500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-37000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-33800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-18800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-8100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-44700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-27500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-66800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-72400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-73700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-69900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-51300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-49300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-779400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-39200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-34400</v>
       </c>
-      <c r="Y94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6482,8 +6715,9 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6497,7 +6731,7 @@
         <v>3500</v>
       </c>
       <c r="G96" s="3">
-        <v>3400</v>
+        <v>3500</v>
       </c>
       <c r="H96" s="3">
         <v>3400</v>
@@ -6509,13 +6743,13 @@
         <v>3400</v>
       </c>
       <c r="K96" s="3">
+        <v>3400</v>
+      </c>
+      <c r="L96" s="3">
         <v>6300</v>
       </c>
-      <c r="L96" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M96" s="3">
-        <v>3100</v>
+      <c r="M96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N96" s="3">
         <v>3100</v>
@@ -6527,7 +6761,7 @@
         <v>3100</v>
       </c>
       <c r="Q96" s="3">
-        <v>0</v>
+        <v>3100</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -6556,8 +6790,11 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6630,8 +6867,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6704,8 +6944,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6778,82 +7021,88 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>71600</v>
+      </c>
+      <c r="E100" s="3">
         <v>15600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>20600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1105300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>316000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-2500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>39200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-19100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>173600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>9900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>10400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>21400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>37800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>30400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>6200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>77700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>43400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>4400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>1132400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>94300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>52000</v>
       </c>
-      <c r="Y100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6896,8 +7145,8 @@
       <c r="P101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -6926,78 +7175,84 @@
       <c r="Z101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-22800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-98500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-28000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-94300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>224900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>76100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>2700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-41800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>122200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-23200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>9600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-19600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-11000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-41200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-47000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-49800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-33500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-22000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-36800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>283200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>30900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-16000</v>
       </c>
-      <c r="Y102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
